--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484288_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484288_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1315</v>
+        <v>5.1998</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2267</v>
+        <v>6.1861</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0953</v>
+        <v>-0.9863</v>
       </c>
       <c r="G2" t="n">
         <v>0.5058</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4303</v>
+        <v>0.4987</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0167</v>
+        <v>-0.0239</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4136</v>
+        <v>0.5226</v>
       </c>
       <c r="V2" t="n">
         <v>2.4373</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7354</v>
+        <v>4.1579</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8066</v>
+        <v>5.6649</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0712</v>
+        <v>-1.507</v>
       </c>
       <c r="G3" t="n">
         <v>3.2484</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3382</v>
+        <v>0.7607</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4404</v>
+        <v>0.2987</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8978</v>
+        <v>0.4621</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2186</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7679</v>
+        <v>2.406</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3641</v>
+        <v>2.4652</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4038</v>
+        <v>-0.0592</v>
       </c>
       <c r="G4" t="n">
         <v>2.1219</v>
@@ -766,13 +766,13 @@
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1354</v>
+        <v>-0.4973</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6657</v>
+        <v>-0.5646</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5303</v>
+        <v>0.0673</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121</v>
+        <v>2.2027</v>
       </c>
       <c r="E5" t="n">
         <v>1.9849</v>
       </c>
       <c r="F5" t="n">
-        <v>0.136</v>
+        <v>0.2177</v>
       </c>
       <c r="G5" t="n">
         <v>2.5428</v>
@@ -844,13 +844,13 @@
         <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7269</v>
+        <v>-0.6452</v>
       </c>
       <c r="T5" t="n">
         <v>-0.2421</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4848</v>
+        <v>-0.4031</v>
       </c>
       <c r="V5" t="n">
         <v>0.1097</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5022</v>
+        <v>1.8212</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2691</v>
+        <v>1.3702</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2331</v>
+        <v>0.451</v>
       </c>
       <c r="G6" t="n">
         <v>1.8549</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1341</v>
+        <v>-0.8151</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6657</v>
+        <v>-0.5646</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4683</v>
+        <v>-0.2504</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.97</v>
+        <v>1.4516</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4487</v>
+        <v>2.2453</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4787</v>
+        <v>-0.7937</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4533</v>
+        <v>2.1938</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7669</v>
+        <v>-0.6657</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6863</v>
+        <v>2.8594</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2314</v>
+        <v>4.2371</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6001</v>
+        <v>-0.2418</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6313</v>
+        <v>4.4789</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7781</v>
+        <v>-2.0433</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.4239</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9449</v>
+        <v>-1.6194</v>
       </c>
       <c r="P7" t="n">
         <v>-0.7814</v>
@@ -1000,28 +1000,28 @@
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5167</v>
+        <v>0.3164</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5614</v>
+        <v>-0.0384</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0447</v>
+        <v>0.3548</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8279</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4732</v>
+        <v>1.0462</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3758</v>
+        <v>3.307</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9026</v>
+        <v>-2.2608</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1938</v>
+        <v>2.4533</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6657</v>
+        <v>0.7669</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8594</v>
+        <v>1.6863</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2371</v>
+        <v>4.2314</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2418</v>
+        <v>1.6001</v>
       </c>
       <c r="L8" t="n">
-        <v>4.4789</v>
+        <v>2.6313</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0433</v>
+        <v>-1.7781</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4239</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6194</v>
+        <v>-0.9449</v>
       </c>
       <c r="P8" t="n">
         <v>-0.7814</v>
@@ -1078,28 +1078,28 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.662</v>
+        <v>0.5929</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.4197</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2458</v>
+        <v>0.1732</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8694</v>
+        <v>-1.2191</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9148</v>
+        <v>0.116</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0454</v>
+        <v>-1.3351</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4526</v>
+        <v>-2.4377</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4249</v>
+        <v>-0.3876</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0276</v>
+        <v>-2.0501</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1026</v>
+        <v>-1.1438</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3454</v>
+        <v>-0.0384</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2428</v>
+        <v>-1.1054</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.35</v>
+        <v>-1.2939</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0795</v>
+        <v>-0.3492</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2704</v>
+        <v>-0.9447</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0847</v>
+        <v>-0.7814</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1127</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.028</v>
+        <v>0.0054</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3321</v>
+        <v>2.4373</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.328</v>
+        <v>-1.2194</v>
       </c>
       <c r="E10" t="n">
-        <v>0.116</v>
+        <v>-2.3192</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.444</v>
+        <v>1.0999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4377</v>
+        <v>-0.4526</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3876</v>
+        <v>-0.4249</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0501</v>
+        <v>-0.0276</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1438</v>
+        <v>-0.1026</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0384</v>
+        <v>-0.3454</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1054</v>
+        <v>0.2428</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2939</v>
+        <v>-0.35</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3492</v>
+        <v>-0.0795</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9447</v>
+        <v>-0.2704</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8903</v>
+        <v>-0.4347</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5172</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1035</v>
+        <v>0.0824</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4373</v>
+        <v>-0.3321</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3293</v>
+        <v>-2.2282</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1107</v>
+        <v>-1.0095</v>
       </c>
       <c r="F11" t="n">
         <v>-1.2186</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9291</v>
+        <v>-3.0708</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4693</v>
+        <v>0.3275</v>
       </c>
       <c r="F12" t="n">
         <v>-3.3983</v>
@@ -1390,10 +1390,10 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6741</v>
+        <v>0.5324</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5614</v>
+        <v>0.4197</v>
       </c>
       <c r="U12" t="n">
         <v>0.1127</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.2454</v>
+        <v>10.5479</v>
       </c>
       <c r="E13" t="n">
-        <v>20.0357</v>
+        <v>20.3384</v>
       </c>
       <c r="F13" t="n">
         <v>-9.790399999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>9.465600000000002</v>
+        <v>9.4656</v>
       </c>
       <c r="H13" t="n">
         <v>-1.9981</v>
@@ -1453,7 +1453,7 @@
         <v>-16.7094</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.9119</v>
+        <v>-5.911900000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-10.7974</v>
@@ -1468,22 +1468,22 @@
         <v>11.7207</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6741</v>
+        <v>-0.3714999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8009</v>
+        <v>-1.4984</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1269</v>
+        <v>1.127</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4994999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>5.428999999999999</v>
+        <v>5.429</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.928500000000001</v>
+        <v>-5.9285</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1789</v>
+        <v>1.564</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8065</v>
+        <v>2.1099</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6276</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>0.6753</v>
@@ -1546,13 +1546,13 @@
         <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1876</v>
+        <v>0.1974</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4099</v>
+        <v>-0.1065</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2223</v>
+        <v>0.304</v>
       </c>
       <c r="V14" t="n">
         <v>0.8865</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0044</v>
+        <v>1.0626</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5162</v>
+        <v>0.8196</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4881</v>
+        <v>0.243</v>
       </c>
       <c r="G15" t="n">
         <v>0.6836</v>
@@ -1624,13 +1624,13 @@
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1254</v>
+        <v>0.1837</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6096</v>
+        <v>0.3645</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.099</v>
+        <v>0.4527</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3448</v>
+        <v>3.5637</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4438</v>
+        <v>-3.1111</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6979</v>
+        <v>-2.8989</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2059</v>
+        <v>-1.0113</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9039</v>
+        <v>-1.8877</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8441</v>
+        <v>1.9962</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4323</v>
+        <v>0.1061</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4118</v>
+        <v>1.89</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.1461</v>
+        <v>-4.8951</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6382</v>
+        <v>-1.1174</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.5079</v>
+        <v>-3.7777</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5783</v>
+        <v>-0.456</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5226</v>
+        <v>-0.2866</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0557</v>
+        <v>-0.1694</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>5.7611</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>5.7611</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.328</v>
+        <v>0.0838</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5859</v>
+        <v>3.4459</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9139</v>
+        <v>-3.3621</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3568</v>
+        <v>0.6979</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3815</v>
+        <v>-0.2059</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7382</v>
+        <v>0.9039</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0499</v>
+        <v>4.8441</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8199</v>
+        <v>0.4323</v>
       </c>
       <c r="L17" t="n">
-        <v>0.23</v>
+        <v>4.4118</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4067</v>
+        <v>-4.1461</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4384</v>
+        <v>-0.6382</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.9682</v>
+        <v>-3.5079</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8567</v>
+        <v>-0.3955</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2588</v>
+        <v>-0.4215</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5979</v>
+        <v>0.026</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8659</v>
+        <v>-1.0321</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6537</v>
+        <v>1.1814</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5196</v>
+        <v>-2.2135</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8989</v>
+        <v>-2.3568</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0113</v>
+        <v>0.3815</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8877</v>
+        <v>-2.7382</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9962</v>
+        <v>1.0499</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1061</v>
+        <v>0.8199</v>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>0.23</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.8951</v>
+        <v>-3.4067</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1174</v>
+        <v>-0.4384</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.7777</v>
+        <v>-2.9682</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7746</v>
+        <v>0.1527</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1967</v>
+        <v>-0.1457</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5779</v>
+        <v>0.2983</v>
       </c>
       <c r="V18" t="n">
-        <v>5.7611</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>5.7611</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7626</v>
+        <v>-1.6497</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5072</v>
+        <v>-1.8902</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2699</v>
+        <v>0.2405</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4697</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3262</v>
+        <v>-2.1753</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7959000000000001</v>
+        <v>1.578</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7493</v>
+        <v>0.0219</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0614</v>
+        <v>-1.9609</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>1.9828</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.219</v>
+        <v>-0.6192</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2648</v>
+        <v>-0.2144</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4838</v>
+        <v>-0.4049</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0743</v>
+        <v>0.315</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2421</v>
+        <v>0.0413</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1678</v>
+        <v>0.2737</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8844</v>
+        <v>-1.7626</v>
       </c>
       <c r="E20" t="n">
-        <v>1.168</v>
+        <v>0.5072</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0524</v>
+        <v>-2.2699</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7196</v>
+        <v>-0.4697</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2469</v>
+        <v>0.3262</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.9664</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8871</v>
+        <v>0.7493</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8851</v>
+        <v>0.0614</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002</v>
+        <v>0.6879</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.6067</v>
+        <v>-1.219</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6382</v>
+        <v>0.2648</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.9684</v>
+        <v>-1.4838</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4677</v>
+        <v>-0.0743</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2343</v>
+        <v>-0.2421</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2334</v>
+        <v>0.1678</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2992</v>
+        <v>-4.2104</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2946</v>
+        <v>-0.4498</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0046</v>
+        <v>-3.7605</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-2.7196</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1753</v>
+        <v>0.2469</v>
       </c>
       <c r="I21" t="n">
-        <v>1.578</v>
+        <v>-2.9664</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0219</v>
+        <v>0.8871</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9609</v>
+        <v>0.8851</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9828</v>
+        <v>0.002</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6192</v>
+        <v>-3.6067</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2144</v>
+        <v>-0.6382</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4049</v>
+        <v>-2.9684</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3345</v>
+        <v>1.1418</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3631</v>
+        <v>0.6165</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0286</v>
+        <v>0.5253</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1894</v>
+        <v>-4.7536</v>
       </c>
       <c r="E22" t="n">
         <v>0.5027</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.6921</v>
+        <v>-5.2564</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4802</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8264</v>
+        <v>-0.3907</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4015</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4249</v>
+        <v>0.0108</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8828</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.2452</v>
+        <v>-10.2453</v>
       </c>
       <c r="E23" t="n">
-        <v>9.790400000000002</v>
+        <v>9.7904</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.0358</v>
+        <v>-20.0359</v>
       </c>
       <c r="G23" t="n">
         <v>-9.465699999999998</v>
@@ -2245,19 +2245,19 @@
         <v>-11.7205</v>
       </c>
       <c r="R23" t="n">
-        <v>9.767200000000001</v>
+        <v>9.767199999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6740999999999995</v>
+        <v>0.6740999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.127</v>
+        <v>-1.1269</v>
       </c>
       <c r="U23" t="n">
-        <v>1.8011</v>
+        <v>1.801</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4996000000000005</v>
+        <v>0.4995999999999996</v>
       </c>
       <c r="W23" t="n">
         <v>5.928599999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484288_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484288_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.406</v>
+        <v>2.2027</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4652</v>
+        <v>1.9849</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0592</v>
+        <v>0.2177</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1219</v>
+        <v>2.5428</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6562</v>
+        <v>0.1962</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7781</v>
+        <v>2.3466</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4205</v>
+        <v>2.6177</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1023</v>
+        <v>0.6754</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3182</v>
+        <v>1.9424</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2986</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7585</v>
+        <v>-0.4792</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5401</v>
+        <v>0.4043</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.3907</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4973</v>
+        <v>-0.6452</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5646</v>
+        <v>-0.2421</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0673</v>
+        <v>-0.4031</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1097</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2027</v>
+        <v>1.8212</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9849</v>
+        <v>1.3702</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2177</v>
+        <v>0.451</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5428</v>
+        <v>1.8549</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1962</v>
+        <v>0.573</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3466</v>
+        <v>1.2819</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6177</v>
+        <v>2.1302</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6754</v>
+        <v>0.3083</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9424</v>
+        <v>1.8219</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.2753</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4792</v>
+        <v>0.2648</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4043</v>
+        <v>-0.5401</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6452</v>
+        <v>-0.8151</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2421</v>
+        <v>-0.5646</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4031</v>
+        <v>-0.2504</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1097</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1097</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8212</v>
+        <v>1.4516</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3702</v>
+        <v>2.2453</v>
       </c>
       <c r="F6" t="n">
-        <v>0.451</v>
+        <v>-0.7937</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8549</v>
+        <v>2.1938</v>
       </c>
       <c r="H6" t="n">
-        <v>0.573</v>
+        <v>-0.6657</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2819</v>
+        <v>2.8594</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1302</v>
+        <v>4.2371</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3083</v>
+        <v>-0.2418</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8219</v>
+        <v>4.4789</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2753</v>
+        <v>-2.0433</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2648</v>
+        <v>-0.4239</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5401</v>
+        <v>-1.6194</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8151</v>
+        <v>0.3164</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5646</v>
+        <v>-0.0384</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2504</v>
+        <v>0.3548</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4516</v>
+        <v>1.214</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2453</v>
+        <v>1.214</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7937</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1938</v>
+        <v>1.214</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6657</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8594</v>
+        <v>1.214</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2371</v>
+        <v>1.214</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2418</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4.4789</v>
+        <v>1.214</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0433</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4239</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6194</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3164</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0384</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3548</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0462</v>
+        <v>1.192</v>
       </c>
       <c r="E8" t="n">
-        <v>3.307</v>
+        <v>1.2512</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2608</v>
+        <v>-0.0592</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4533</v>
+        <v>0.908</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7669</v>
+        <v>-0.6562</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6863</v>
+        <v>1.5641</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2314</v>
+        <v>2.2065</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6001</v>
+        <v>0.1023</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6313</v>
+        <v>2.1042</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7781</v>
+        <v>-1.2986</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.7585</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9449</v>
+        <v>-0.5401</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="R8" t="n">
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5929</v>
+        <v>-0.4973</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4197</v>
+        <v>-0.5646</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1732</v>
+        <v>0.0673</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2191</v>
+        <v>1.0462</v>
       </c>
       <c r="E9" t="n">
-        <v>0.116</v>
+        <v>3.307</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3351</v>
+        <v>-2.2608</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4377</v>
+        <v>2.4533</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3876</v>
+        <v>0.7669</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0501</v>
+        <v>1.6863</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1438</v>
+        <v>4.2314</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0384</v>
+        <v>1.6001</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1054</v>
+        <v>2.6313</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2939</v>
+        <v>-1.7781</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3492</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9447</v>
+        <v>-0.9449</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3907</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7814</v>
+        <v>0.5929</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.4197</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0054</v>
+        <v>0.1732</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2186</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4373</v>
+        <v>0.6093</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2194</v>
+        <v>-1.2191</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3192</v>
+        <v>0.116</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0999</v>
+        <v>-1.3351</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4526</v>
+        <v>-2.4377</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4249</v>
+        <v>-0.3876</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0276</v>
+        <v>-2.0501</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1026</v>
+        <v>-1.1438</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3454</v>
+        <v>-0.0384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2428</v>
+        <v>-1.1054</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.35</v>
+        <v>-1.2939</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0795</v>
+        <v>-0.3492</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2704</v>
+        <v>-0.9447</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4347</v>
+        <v>-0.7814</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5172</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0824</v>
+        <v>0.0054</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3321</v>
+        <v>2.4373</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2282</v>
+        <v>-1.2194</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0095</v>
+        <v>-2.3192</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2186</v>
+        <v>1.0999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1572</v>
+        <v>-0.4526</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3479</v>
+        <v>-0.4249</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8093</v>
+        <v>-0.0276</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0614</v>
+        <v>-0.1026</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0614</v>
+        <v>-0.3454</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.2428</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2186</v>
+        <v>-0.35</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4093</v>
+        <v>-0.0795</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8093</v>
+        <v>-0.2704</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1011</v>
+        <v>-0.4347</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1011</v>
+        <v>-0.5172</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.0824</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0708</v>
+        <v>-2.2282</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3275</v>
+        <v>-1.0095</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3983</v>
+        <v>-1.2186</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4078</v>
+        <v>-1.1572</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4633</v>
+        <v>-0.3479</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9445</v>
+        <v>-0.8093</v>
       </c>
       <c r="J12" t="n">
-        <v>1.584</v>
+        <v>0.0614</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6395</v>
+        <v>0.0614</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9445</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9919</v>
+        <v>-1.2186</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1028</v>
+        <v>-0.4093</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8891</v>
+        <v>-0.8093</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5324</v>
+        <v>0.1011</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4197</v>
+        <v>0.1011</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1127</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.5479</v>
+        <v>-3.0708</v>
       </c>
       <c r="E13" t="n">
-        <v>20.3384</v>
+        <v>0.3275</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.790399999999998</v>
+        <v>-3.3983</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4656</v>
+        <v>-1.4078</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9981</v>
+        <v>-0.4633</v>
       </c>
       <c r="I13" t="n">
-        <v>11.4637</v>
+        <v>-0.9445</v>
       </c>
       <c r="J13" t="n">
-        <v>26.1749</v>
+        <v>1.584</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9138</v>
+        <v>0.6395</v>
       </c>
       <c r="L13" t="n">
-        <v>22.2611</v>
+        <v>0.9445</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.7094</v>
+        <v>-2.9919</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.911900000000001</v>
+        <v>-1.1028</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.7974</v>
+        <v>-1.8891</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.767099999999999</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>11.7207</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3714999999999999</v>
+        <v>0.5324</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4984</v>
+        <v>0.4197</v>
       </c>
       <c r="U13" t="n">
-        <v>1.127</v>
+        <v>0.1127</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4994999999999998</v>
+        <v>-1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>5.429</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.9285</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.564</v>
+        <v>10.5479</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1099</v>
+        <v>20.3384</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-9.790399999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6753</v>
+        <v>9.465700000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4426</v>
+        <v>-1.9981</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7673</v>
+        <v>11.4637</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6387</v>
+        <v>26.1749</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5173</v>
+        <v>3.9138</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1214</v>
+        <v>22.2611</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9634</v>
+        <v>-16.7094</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0747</v>
+        <v>-5.911900000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8887</v>
+        <v>-10.7974</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-9.767100000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7814</v>
+        <v>11.7207</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1974</v>
+        <v>-0.3714999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1065</v>
+        <v>-1.4984</v>
       </c>
       <c r="U14" t="n">
-        <v>0.304</v>
+        <v>1.127</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8865</v>
+        <v>-0.4995000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>5.429</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3321</v>
-      </c>
+        <v>-5.928500000000001</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0626</v>
+        <v>1.564</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8196</v>
+        <v>2.1099</v>
       </c>
       <c r="F15" t="n">
-        <v>0.243</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6836</v>
+        <v>0.6753</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5574</v>
+        <v>2.4426</v>
       </c>
       <c r="I15" t="n">
-        <v>1.241</v>
+        <v>-1.7673</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9771</v>
+        <v>2.6387</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0614</v>
+        <v>2.5173</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9157</v>
+        <v>0.1214</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2935</v>
+        <v>-1.9634</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6188</v>
+        <v>-0.0747</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6747</v>
+        <v>-1.8887</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1837</v>
+        <v>0.1974</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1808</v>
+        <v>-0.1065</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3645</v>
+        <v>0.304</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4527</v>
+        <v>1.521</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5637</v>
+        <v>1.521</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1111</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8989</v>
+        <v>1.521</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0113</v>
+        <v>0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8877</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9962</v>
+        <v>1.521</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1061</v>
+        <v>0.307</v>
       </c>
       <c r="L16" t="n">
-        <v>1.89</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.8951</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1174</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.7777</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.456</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2866</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1694</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7611</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>5.7611</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0838</v>
+        <v>1.0626</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4459</v>
+        <v>0.8196</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3621</v>
+        <v>0.243</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6979</v>
+        <v>0.6836</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2059</v>
+        <v>-0.5574</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9039</v>
+        <v>1.241</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8441</v>
+        <v>1.9771</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4323</v>
+        <v>0.0614</v>
       </c>
       <c r="L17" t="n">
-        <v>4.4118</v>
+        <v>1.9157</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.1461</v>
+        <v>-1.2935</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6382</v>
+        <v>-0.6188</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.5079</v>
+        <v>-0.6747</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3955</v>
+        <v>0.1837</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4215</v>
+        <v>-0.1808</v>
       </c>
       <c r="U17" t="n">
-        <v>0.026</v>
+        <v>0.3645</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0321</v>
+        <v>0.4527</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1814</v>
+        <v>3.5637</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2135</v>
+        <v>-3.1111</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3568</v>
+        <v>-2.8989</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3815</v>
+        <v>-1.0113</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7382</v>
+        <v>-1.8877</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0499</v>
+        <v>1.9962</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8199</v>
+        <v>0.1061</v>
       </c>
       <c r="L18" t="n">
-        <v>0.23</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.4067</v>
+        <v>-4.8951</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4384</v>
+        <v>-1.1174</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.9682</v>
+        <v>-3.7777</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1527</v>
+        <v>-0.456</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1457</v>
+        <v>-0.2866</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2983</v>
+        <v>-0.1694</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.7611</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>5.7611</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6497</v>
+        <v>0.0838</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8902</v>
+        <v>3.4459</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2405</v>
+        <v>-3.3621</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0.6979</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1753</v>
+        <v>-0.2059</v>
       </c>
       <c r="I19" t="n">
-        <v>1.578</v>
+        <v>0.9039</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0219</v>
+        <v>4.8441</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9609</v>
+        <v>0.4323</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9828</v>
+        <v>4.4118</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6192</v>
+        <v>-4.1461</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2144</v>
+        <v>-0.6382</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4049</v>
+        <v>-3.5079</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>0.315</v>
+        <v>-0.3955</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0413</v>
+        <v>-0.4215</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2737</v>
+        <v>0.026</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7626</v>
+        <v>-1.0321</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5072</v>
+        <v>1.1814</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2699</v>
+        <v>-2.2135</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4697</v>
+        <v>-2.3568</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3262</v>
+        <v>0.3815</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-2.7382</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7493</v>
+        <v>1.0499</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0614</v>
+        <v>0.8199</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6879</v>
+        <v>0.23</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.219</v>
+        <v>-3.4067</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2648</v>
+        <v>-0.4384</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4838</v>
+        <v>-2.9682</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0743</v>
+        <v>0.1527</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2421</v>
+        <v>-0.1457</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1678</v>
+        <v>0.2983</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2104</v>
+        <v>-1.6497</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4498</v>
+        <v>-1.8902</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7605</v>
+        <v>0.2405</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7196</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2469</v>
+        <v>-2.1753</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9664</v>
+        <v>1.578</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8871</v>
+        <v>0.0219</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8851</v>
+        <v>-1.9609</v>
       </c>
       <c r="L21" t="n">
-        <v>0.002</v>
+        <v>1.9828</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6067</v>
+        <v>-0.6192</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6382</v>
+        <v>-0.2144</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9684</v>
+        <v>-0.4049</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1418</v>
+        <v>0.315</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6165</v>
+        <v>0.0413</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5253</v>
+        <v>0.2737</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7536</v>
+        <v>-1.7626</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5027</v>
+        <v>0.5072</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.2564</v>
+        <v>-2.2699</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4802</v>
+        <v>-0.4697</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5508</v>
+        <v>0.3262</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.031</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5451</v>
+        <v>0.7493</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9893</v>
+        <v>0.0614</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4441</v>
+        <v>0.6879</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.0253</v>
+        <v>-1.219</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4384</v>
+        <v>0.2648</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.5868</v>
+        <v>-1.4838</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3907</v>
+        <v>-0.0743</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4015</v>
+        <v>-0.2421</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0108</v>
+        <v>0.1678</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8828</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.2453</v>
+        <v>-4.7536</v>
       </c>
       <c r="E23" t="n">
-        <v>9.7904</v>
+        <v>0.5027</v>
       </c>
       <c r="F23" t="n">
+        <v>-5.2564</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.4802</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.5508</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-5.031</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.5451</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.9893</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.4441</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-5.0253</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.4384</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-4.5868</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.4015</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. GARCIA RIERA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5.7313</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.9708</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-3.7605</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-4.2405</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.0601</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-4.1804</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.6339</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.212</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-3.6067</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.6382</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-2.9684</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.1418</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.6165</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484288_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-10.2452</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.790400000000002</v>
+      </c>
+      <c r="F25" t="n">
         <v>-20.0359</v>
       </c>
-      <c r="G23" t="n">
-        <v>-9.465699999999998</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="G25" t="n">
+        <v>-9.4656</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.9981</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>-11.4636</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>16.7094</v>
       </c>
-      <c r="K23" t="n">
-        <v>5.911899999999999</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K25" t="n">
+        <v>5.9119</v>
+      </c>
+      <c r="L25" t="n">
         <v>10.7975</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>-26.175</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-3.9137</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-22.2611</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>-1.9533</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-11.7205</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>9.767199999999999</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>0.6740999999999999</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>-1.1269</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>1.801</v>
       </c>
-      <c r="V23" t="n">
-        <v>0.4995999999999996</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V25" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="W25" t="n">
         <v>5.928599999999999</v>
       </c>
-      <c r="X23" t="n">
-        <v>-5.428900000000001</v>
-      </c>
+      <c r="X25" t="n">
+        <v>-5.4289</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
